--- a/VerveStacks_SVK_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_SVK_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SVK_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA1A4DB-C32B-48DA-9CA5-326D5BBA3A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C22C380-B77B-4D1A-84E4-916D4ED1B447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3590,7 +3590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AF402E-8338-4D54-8205-97D8130C0DEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{021E21A6-BE93-4B86-9969-3E3F3B1F5D73}">
   <dimension ref="B3:I61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
